--- a/data/seed/portfolio/L-2025-0391/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2025-0391/vypiska_2026-07_09.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I178"/>
+  <dimension ref="A1:I172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -550,7 +550,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>02.07.2026</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -560,38 +560,38 @@
       </c>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n">
-        <v>31841000</v>
+        <v>7392000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Guliston Metall Servis MChJ</t>
+          <t>Jizzax Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>375524438</t>
+          <t>242429802</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000001652700001</t>
+          <t>20208000781244145001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2337 от 02.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по договору 151/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>02.07.2026</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -601,31 +601,31 @@
       </c>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n">
-        <v>22432000</v>
+        <v>6755000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Namangan Yog'och MChJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>217915651</t>
+          <t>267217193</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000496888330001</t>
+          <t>20208000332723654001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №235/26, QQS 12%</t>
+          <t>Оплата за товар по счет-фактуре №352 от 01.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -640,40 +640,40 @@
           <t>102</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>28577000</v>
-      </c>
-      <c r="D12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n">
+        <v>11561000</v>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chirchiq Qurilish MChJ</t>
+          <t>Gulshan Sut Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>306978170</t>
+          <t>352443850</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000935712209001</t>
+          <t>20208000165270044001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №289/26</t>
+          <t>Оплата за продукцию по договору №36/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>02.07.2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -682,39 +682,39 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>89985000</v>
+        <v>41400000</v>
       </c>
       <c r="D13" s="2" t="n"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shodlik Agro MChJ</t>
+          <t>Navoiy Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>277461122</t>
+          <t>390107567</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000801642805001</t>
+          <t>20208000876402081001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №92/26, QQS bilan</t>
+          <t>Оплата за транспортные услуги по договору №197/26</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>03.07.2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -722,40 +722,40 @@
           <t>104</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n">
-        <v>39047000</v>
-      </c>
+      <c r="C14" s="2" t="n">
+        <v>16076000</v>
+      </c>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Namangan Yog'och MChJ</t>
+          <t>Farg'ona Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>217915651</t>
+          <t>221596651</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000496888330001</t>
+          <t>20208000427736682001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №88/26 от 06.07.2026</t>
+          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО С/Ф №9419</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>03.07.2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -763,33 +763,33 @@
           <t>105</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n">
-        <v>13541000</v>
-      </c>
+      <c r="C15" s="2" t="n">
+        <v>21853000</v>
+      </c>
+      <c r="D15" s="2" t="n"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Bog'ishamol Metall XK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>300463501</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000591046906001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №276</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №57/26, QQS bilan</t>
         </is>
       </c>
     </row>
@@ -806,31 +806,31 @@
       </c>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n">
-        <v>8069000</v>
+        <v>65314000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Shartnoma №176/26 bo'yicha oldindan to'lov</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9287</t>
         </is>
       </c>
     </row>
@@ -847,31 +847,31 @@
       </c>
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="n">
-        <v>7152000</v>
+        <v>17284000</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tong Tikuv MChJ</t>
+          <t>Nihol Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>280547772</t>
+          <t>391565114</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000712235315001</t>
+          <t>20208000688833047001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №1672 06.07.2026, QQS BILAN</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №3024 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
     </row>
@@ -888,31 +888,31 @@
       </c>
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="n">
-        <v>6266000</v>
+        <v>9245000</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bog'ishamol Logistik AJ</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>394672171</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000353327236001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №117/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №1252 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -927,33 +927,33 @@
           <t>109</t>
         </is>
       </c>
-      <c r="C19" s="2" t="n">
-        <v>13400000</v>
-      </c>
-      <c r="D19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n">
+        <v>3645000</v>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Xiva Savdo AJ</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>276141163</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000172772008001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №2041</t>
+          <t>Предоплата за товар по договору №194/26 от 06.07.2026</t>
         </is>
       </c>
     </row>
@@ -969,27 +969,32 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>28962000</v>
+        <v>19861000</v>
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Farg'ona Qurilish MChJ</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>241127198</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000948653694001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Iyun oyi uchun ish haqi, reestr №1432</t>
+          <t>Оплата за товары согласно счет-фактуре №3900</t>
         </is>
       </c>
     </row>
@@ -1005,22 +1010,17 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>86887000</v>
+        <v>28962000</v>
       </c>
       <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Xiva Savdo AJ</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>276141163</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000172772008001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1030,14 +1030,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №159/26</t>
+          <t>Перечисление заработной платы за июнь 2026 г. согласно реестру №7138</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1045,33 +1045,33 @@
           <t>112</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n">
-        <v>19323000</v>
-      </c>
+      <c r="C22" s="2" t="n">
+        <v>92653000</v>
+      </c>
+      <c r="D22" s="2" t="n"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Shahrisabz Meva-Sabzavot AJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>244144970</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000827779009001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7849 07.07.2026, QQS bilan</t>
+          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №1968</t>
         </is>
       </c>
     </row>
@@ -1088,38 +1088,38 @@
       </c>
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="n">
-        <v>8629000</v>
+        <v>4330000</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №291/26, QQS 12%</t>
+          <t>Предоплата за товар по договору №117/26 от 07.07.2026</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07.07.2026</t>
+          <t>08.07.2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1129,38 +1129,38 @@
       </c>
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="n">
-        <v>5878000</v>
+        <v>12702000</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Afrosiyob Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>254777237</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000223531516001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Shartnoma №150/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по с/ф №7653 от 08.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07.07.2026</t>
+          <t>08.07.2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1168,33 +1168,33 @@
           <t>115</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
-        <v>5084000</v>
-      </c>
-      <c r="D25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n">
+        <v>5909000</v>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zafar Qurilish Materiallari MChJ</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>378144144</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000702827779001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Арендная плата за июль 2026 г. по дог. №6/25</t>
+          <t>Оплата по счет-фактуре №6350 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -1209,33 +1209,33 @@
           <t>116</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n">
-        <v>58390000</v>
-      </c>
+      <c r="C26" s="2" t="n">
+        <v>5084000</v>
+      </c>
+      <c r="D26" s="2" t="n"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Namangan Yog'och MChJ</t>
+          <t>Yangi Hayot Qurilish MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>217915651</t>
+          <t>281427108</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000496888330001</t>
+          <t>20208000189581100001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Shartnoma №83/26 bo'yicha oldindan to'lov</t>
+          <t>Аренда помещения за июль, до. №34/20</t>
         </is>
       </c>
     </row>
@@ -1251,32 +1251,32 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>12636000</v>
+        <v>20613000</v>
       </c>
       <c r="D27" s="2" t="n"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mehnat Mebel MChJ</t>
+          <t>Shahrisabz Meva-Sabzavot AJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>280843314</t>
+          <t>244144970</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000711222925001</t>
+          <t>20208000827779009001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №245/26</t>
+          <t>Оплата за транспортные услуги по договору №108/26</t>
         </is>
       </c>
     </row>
@@ -1293,31 +1293,31 @@
       </c>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n">
-        <v>42749000</v>
+        <v>6667000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tong Tikuv MChJ</t>
+          <t>Nihol Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>280547772</t>
+          <t>391565114</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000712235315001</t>
+          <t>20208000688833047001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №19/26 от 09.07.2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №835</t>
         </is>
       </c>
     </row>
@@ -1334,38 +1334,38 @@
       </c>
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="n">
-        <v>48797000</v>
+        <v>4067000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>267217193</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000332723654001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Shartnoma №264/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по договору №212/26 от 10.07.2026</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1375,31 +1375,31 @@
       </c>
       <c r="C30" s="2" t="n"/>
       <c r="D30" s="2" t="n">
-        <v>11056000</v>
+        <v>52379000</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ilhom Agro Servis MChJ</t>
+          <t>Afrosiyob Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>246491058</t>
+          <t>254777237</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000123905116001</t>
+          <t>20208000223531516001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №5730 10.07.2026, QQS bilan</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО С/Ф №9156 ОТ 13.07.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -1416,21 +1416,21 @@
       </c>
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="n">
-        <v>19390000</v>
+        <v>11340000</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Namangan Yog'och MChJ</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>217915651</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000496888330001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uhun to'lov h/f №3282</t>
+          <t>Оплата за товар по с/ф №6740 от 13.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -1457,31 +1457,31 @@
       </c>
       <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="n">
-        <v>13595000</v>
+        <v>4223000</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1831 13.7.2026, QQS bilan</t>
+          <t>Оплата за продукцию по дог. №130/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -1496,40 +1496,40 @@
           <t>123</t>
         </is>
       </c>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n">
-        <v>6970000</v>
-      </c>
+      <c r="C33" s="2" t="n">
+        <v>16927000</v>
+      </c>
+      <c r="D33" s="2" t="n"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tong Tikuv MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>280547772</t>
+          <t>241127198</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000712235315001</t>
+          <t>20208000948653694001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №128/26, QQS 12%</t>
+          <t>Оплата за сырье по договору №76/26 от 13.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1538,39 +1538,39 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>11509000</v>
+        <v>3949000</v>
       </c>
       <c r="D34" s="2" t="n"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Chirchiq Qurilish MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>306978170</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000935712209001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №256/26</t>
+          <t>Уплата социального налога за июнь</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1579,39 +1579,39 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>13787000</v>
+        <v>3949000</v>
       </c>
       <c r="D35" s="2" t="n"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Chirchiq Qurilish MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>306978170</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000935712209001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №291/26</t>
+          <t>НДФЛ за июнь 2026</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1619,33 +1619,33 @@
           <t>126</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n">
-        <v>23901000</v>
-      </c>
+      <c r="C36" s="2" t="n">
+        <v>23023000</v>
+      </c>
+      <c r="D36" s="2" t="n"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Shahrisabz Meva-Sabzavot AJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>244144970</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000827779009001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Shartnoma №154/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за сырье по договору №43/26 от 15.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -1660,33 +1660,33 @@
           <t>127</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n">
-        <v>3949000</v>
-      </c>
-      <c r="D37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n">
+        <v>5542000</v>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Уплата социального налога за июнь</t>
+          <t>Shartnoma №251/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
@@ -1702,39 +1702,39 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>3949000</v>
+        <v>21877000</v>
       </c>
       <c r="D38" s="2" t="n"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Angren Plastik MChJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>335430118</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000388392086001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Jismoniy shaxslar daromad solig'i iyun 2026</t>
+          <t>Оплата за сырье по договору №132/26 от 16.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1742,33 +1742,33 @@
           <t>129</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n">
-        <v>198399000</v>
-      </c>
-      <c r="D39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n">
+        <v>23744000</v>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Xiva Savdo AJ</t>
+          <t>Shahrisabz Mato XK</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>276141163</t>
+          <t>314116341</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000172772008001</t>
+          <t>20208000277200827001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №154/26</t>
+          <t>Оплата по с/ф №5648 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -1783,23 +1783,18 @@
           <t>130</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n">
-        <v>21175000</v>
-      </c>
+      <c r="C40" s="2" t="n">
+        <v>42000000</v>
+      </c>
+      <c r="D40" s="2" t="n"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>328917343</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-0391)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>16307000368529438417</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1809,7 +1804,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №280/26, QQS 12%</t>
+          <t>Kredit shartnomasi L-2025-0391 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
     </row>
@@ -1824,33 +1819,33 @@
           <t>131</t>
         </is>
       </c>
-      <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2" t="n">
-        <v>14736000</v>
-      </c>
+      <c r="C41" s="2" t="n">
+        <v>95777000</v>
+      </c>
+      <c r="D41" s="2" t="n"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Navoiy Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>390107567</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000876402081001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9863 от 20.07.2026, в т.ч. НДС 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №242/26, QQS bilan</t>
         </is>
       </c>
     </row>
@@ -1866,22 +1861,22 @@
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>18358000</v>
+        <v>131973000</v>
       </c>
       <c r="D42" s="2" t="n"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Xiva Savdo AJ</t>
+          <t>Angren Plastik MChJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>276141163</t>
+          <t>335430118</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000172772008001</t>
+          <t>20208000388392086001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -1891,14 +1886,14 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №725</t>
+          <t>Оплата за товары согласно счет-фактуре №9142</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1906,28 +1901,33 @@
           <t>133</t>
         </is>
       </c>
-      <c r="C43" s="2" t="n">
-        <v>42000000</v>
-      </c>
-      <c r="D43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n">
+        <v>42196000</v>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-0391)</t>
+          <t>Shodlik Qog'oz MChJ</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>16307000368529438417</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-0391 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Предоплата за товар по дог. №109/26 от 21.07.2026</t>
         </is>
       </c>
     </row>
@@ -1944,38 +1944,38 @@
       </c>
       <c r="C44" s="2" t="n"/>
       <c r="D44" s="2" t="n">
-        <v>27709000</v>
+        <v>7960000</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Shahrisabz Mato XK</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>314116341</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000277200827001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Shartnoma №78/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата по счет-фактуре №6972 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1985,38 +1985,38 @@
       </c>
       <c r="C45" s="2" t="n"/>
       <c r="D45" s="2" t="n">
-        <v>25454000</v>
+        <v>158354000</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ilhom Agro Servis MChJ</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>246491058</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000123905116001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №5287 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Mahsulot uchun to'lov, shartnoma №27/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2026,38 +2026,38 @@
       </c>
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="n">
-        <v>9072000</v>
+        <v>15522000</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Afrosiyob Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>254777237</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000223531516001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9873</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №2090 ОТ 23.07.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2065,40 +2065,40 @@
           <t>137</t>
         </is>
       </c>
-      <c r="C47" s="2" t="n">
-        <v>37277000</v>
-      </c>
-      <c r="D47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n">
+        <v>3522000</v>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Chirchiq Qurilish MChJ</t>
+          <t>Zarafshon Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>306978170</t>
+          <t>258570744</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000935712209001</t>
+          <t>20208000606002244001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №8644</t>
+          <t>Mahsulot uchun to'lov, shartnoma №6/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>8541000</v>
+        <v>8081000</v>
       </c>
       <c r="D48" s="2" t="n"/>
       <c r="E48" t="inlineStr">
@@ -2132,14 +2132,14 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Qo'shilgan qiymat solig'i iyun oyi</t>
+          <t>Уплата налога на добавленную стоимость за июнь</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2149,38 +2149,38 @@
       </c>
       <c r="C49" s="2" t="n"/>
       <c r="D49" s="2" t="n">
-        <v>15003000</v>
+        <v>27328000</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Tong Tikuv MChJ</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>280547772</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000712235315001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Оплата за продукцию п договору №261/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №246/26 от 24.07.2026</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2190,38 +2190,38 @@
       </c>
       <c r="C50" s="2" t="n"/>
       <c r="D50" s="2" t="n">
-        <v>6205000</v>
+        <v>12859000</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Afrosiyob Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>254777237</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000223531516001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №288/26, QQS 12%</t>
+          <t>Предоплата за товар по дог. №169/26 от 24.07.2026</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2229,40 +2229,40 @@
           <t>141</t>
         </is>
       </c>
-      <c r="C51" s="2" t="n">
-        <v>21060000</v>
-      </c>
-      <c r="D51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n">
+        <v>4362000</v>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Xiva Savdo AJ</t>
+          <t>Xiva Savdo MChJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>276141163</t>
+          <t>204944148</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000172772008001</t>
+          <t>20208000470388274001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №5645</t>
+          <t>Оплата за товар по счет-фактуре №8413 от 24.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2272,31 +2272,31 @@
       </c>
       <c r="C52" s="2" t="n"/>
       <c r="D52" s="2" t="n">
-        <v>5469000</v>
+        <v>18450000</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3475</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №627</t>
         </is>
       </c>
     </row>
@@ -2313,31 +2313,31 @@
       </c>
       <c r="C53" s="2" t="n"/>
       <c r="D53" s="2" t="n">
-        <v>7964000</v>
+        <v>10147000</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Zarafshon Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>258570744</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000606002244001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6445</t>
+          <t>Оплата за продукцию по договору №64/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -2368,12 +2368,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000094468700001</t>
+          <t>20208000818188088001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2394,39 +2394,39 @@
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>10273000</v>
+        <v>110352000</v>
       </c>
       <c r="D55" s="2" t="n"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Chirchiq Qurilish MChJ</t>
+          <t>Bog'ishamol Metall XK</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>306978170</t>
+          <t>300463501</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000935712209001</t>
+          <t>20208000591046906001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №256/26, QQS bilan</t>
+          <t>Оплата за упаковочные материалы, с/ф №5740</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2434,40 +2434,40 @@
           <t>146</t>
         </is>
       </c>
-      <c r="C56" s="2" t="n">
-        <v>24015000</v>
-      </c>
-      <c r="D56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n">
+        <v>9729000</v>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Mehnat Mebel MChJ</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>280843314</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000711222925001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №78/26</t>
+          <t>Предоплата за товар по договору №66/26 от 29.07.2026</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2477,38 +2477,38 @@
       </c>
       <c r="C57" s="2" t="n"/>
       <c r="D57" s="2" t="n">
-        <v>29844000</v>
+        <v>12010000</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Shartoma №63/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата по счет-фактуре №5124 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2518,38 +2518,38 @@
       </c>
       <c r="C58" s="2" t="n"/>
       <c r="D58" s="2" t="n">
-        <v>21472000</v>
+        <v>4402000</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Gulshan Sut Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>352443850</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000165270044001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №145/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №75/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2559,38 +2559,38 @@
       </c>
       <c r="C59" s="2" t="n"/>
       <c r="D59" s="2" t="n">
-        <v>20699000</v>
+        <v>3835000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Nihol Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>391565114</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000688833047001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6114</t>
+          <t>Оплата за продукцию по договору №111/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2600,38 +2600,38 @@
       </c>
       <c r="C60" s="2" t="n"/>
       <c r="D60" s="2" t="n">
-        <v>39197000</v>
+        <v>42726000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3747 29.07.2026, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №7548 от 31.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2641,38 +2641,38 @@
       </c>
       <c r="C61" s="2" t="n"/>
       <c r="D61" s="2" t="n">
-        <v>18727000</v>
+        <v>31792000</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №251 29.07.2026, QQS bilan</t>
+          <t>Shartnoma №115/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2682,38 +2682,38 @@
       </c>
       <c r="C62" s="2" t="n"/>
       <c r="D62" s="2" t="n">
-        <v>10753000</v>
+        <v>16119000</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Shodlik Metall MChJ</t>
+          <t>Nihol Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>321585707</t>
+          <t>391565114</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000496060022001</t>
+          <t>20208000688833047001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2748 29.07.2026, QQS bilan</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГ. №51/26 ОТ 31.07.2026</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2721,23 +2721,18 @@
           <t>153</t>
         </is>
       </c>
-      <c r="C63" s="2" t="n"/>
-      <c r="D63" s="2" t="n">
-        <v>6470000</v>
-      </c>
+      <c r="C63" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D63" s="2" t="n"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Tong Tikuv MChJ</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>280547772</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000712235315001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2747,7 +2742,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoa №50/26, QQS 12%</t>
+          <t>Комиссия банка за расчетно-кассовое обслуживание за июль</t>
         </is>
       </c>
     </row>
@@ -2762,40 +2757,40 @@
           <t>154</t>
         </is>
       </c>
-      <c r="C64" s="2" t="n"/>
-      <c r="D64" s="2" t="n">
-        <v>44755000</v>
-      </c>
+      <c r="C64" s="2" t="n">
+        <v>23036000</v>
+      </c>
+      <c r="D64" s="2" t="n"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Shahrisabz Meva-Sabzavot AJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>244144970</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000827779009001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6097</t>
+          <t>Предоплата за материалы по договору №152/26</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2803,35 +2798,40 @@
           <t>155</t>
         </is>
       </c>
-      <c r="C65" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D65" s="2" t="n"/>
+      <c r="C65" s="2" t="n"/>
+      <c r="D65" s="2" t="n">
+        <v>7633000</v>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Nihol Agro Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>391565114</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000688833047001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
+          <t>Mahsulot uchun to'lov, shartnoma №11/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2839,40 +2839,40 @@
           <t>156</t>
         </is>
       </c>
-      <c r="C66" s="2" t="n">
-        <v>29316000</v>
-      </c>
-      <c r="D66" s="2" t="n"/>
+      <c r="C66" s="2" t="n"/>
+      <c r="D66" s="2" t="n">
+        <v>6250000</v>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Chirchiq Qurilish MChJ</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>306978170</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000935712209001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №31/26</t>
+          <t>Оплата за товар по счет-фактуре №877 от 03.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2880,33 +2880,33 @@
           <t>157</t>
         </is>
       </c>
-      <c r="C67" s="2" t="n">
-        <v>39522000</v>
-      </c>
-      <c r="D67" s="2" t="n"/>
+      <c r="C67" s="2" t="n"/>
+      <c r="D67" s="2" t="n">
+        <v>5810000</v>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Mehnat Mebel MChJ</t>
+          <t>Oltin Vodiy Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>280843314</t>
+          <t>381299059</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000711222925001</t>
+          <t>20208000255499460001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №3898</t>
+          <t>Оплата за продукцию по договору №108/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -2923,21 +2923,21 @@
       </c>
       <c r="C68" s="2" t="n"/>
       <c r="D68" s="2" t="n">
-        <v>9501000</v>
+        <v>4910000</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Namangan Yog'och MChJ</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>217915651</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000496888330001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договру №294/26, НДС 12%</t>
+          <t>Оплата за товар по с/ф №3394 от 03.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -2962,33 +2962,33 @@
           <t>159</t>
         </is>
       </c>
-      <c r="C69" s="2" t="n">
-        <v>19190000</v>
-      </c>
-      <c r="D69" s="2" t="n"/>
+      <c r="C69" s="2" t="n"/>
+      <c r="D69" s="2" t="n">
+        <v>4050000</v>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Chirchiq Qurilish MChJ</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>306978170</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000935712209001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №97/26</t>
+          <t>Shartnoma №28/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
@@ -3004,39 +3004,39 @@
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>19931000</v>
+        <v>9883000</v>
       </c>
       <c r="D70" s="2" t="n"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Chirchiq Qurilish MChJ</t>
+          <t>Shahrisabz Meva-Sabzavot AJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>306978170</t>
+          <t>244144970</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000935712209001</t>
+          <t>20208000827779009001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №151/26, QQS bilan</t>
+          <t>Оплата за упаковочные материалы, с/ф №2387</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3045,39 +3045,39 @@
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>54295000</v>
+        <v>10193000</v>
       </c>
       <c r="D71" s="2" t="n"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Chirchiq Qurilish MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>306978170</t>
+          <t>241127198</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000935712209001</t>
+          <t>20208000948653694001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №6691</t>
+          <t>Оплата за сырье по договору №251/26 от 04.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3085,35 +3085,40 @@
           <t>162</t>
         </is>
       </c>
-      <c r="C72" s="2" t="n">
-        <v>26375000</v>
-      </c>
-      <c r="D72" s="2" t="n"/>
+      <c r="C72" s="2" t="n"/>
+      <c r="D72" s="2" t="n">
+        <v>10383000</v>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Shodlik Qog'oz MChJ</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi iyul 2026 (plastik kartalarga)</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4465</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3123,31 +3128,31 @@
       </c>
       <c r="C73" s="2" t="n"/>
       <c r="D73" s="2" t="n">
-        <v>95578000</v>
+        <v>4373000</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Tong Tikuv MChJ</t>
+          <t>Jizzax Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>280547772</t>
+          <t>242429802</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000712235315001</t>
+          <t>20208000781244145001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №122/26, QQS 12%</t>
+          <t>Shartnoma №64/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
@@ -3162,23 +3167,18 @@
           <t>164</t>
         </is>
       </c>
-      <c r="C74" s="2" t="n"/>
-      <c r="D74" s="2" t="n">
-        <v>69092000</v>
-      </c>
+      <c r="C74" s="2" t="n">
+        <v>26375000</v>
+      </c>
+      <c r="D74" s="2" t="n"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>328917343</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6784 за поставленный товар</t>
+          <t>Заработная плата за июль 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
     </row>
@@ -3205,38 +3205,38 @@
       </c>
       <c r="C75" s="2" t="n"/>
       <c r="D75" s="2" t="n">
-        <v>23304000</v>
+        <v>7614000</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Buxoro Metall AJ</t>
+          <t>Qo'qon Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>233621625</t>
+          <t>262162550</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000078546127001</t>
+          <t>20208000854612770001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №1106</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №1106 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3246,38 +3246,38 @@
       </c>
       <c r="C76" s="2" t="n"/>
       <c r="D76" s="2" t="n">
-        <v>40509000</v>
+        <v>7375000</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №86/26, QQS 12%</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №5222 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3285,40 +3285,40 @@
           <t>167</t>
         </is>
       </c>
-      <c r="C77" s="2" t="n"/>
-      <c r="D77" s="2" t="n">
-        <v>15822000</v>
-      </c>
+      <c r="C77" s="2" t="n">
+        <v>5388000</v>
+      </c>
+      <c r="D77" s="2" t="n"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Ilhom Agro Servis MChJ</t>
+          <t>Nurafshon Sut Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>246491058</t>
+          <t>282958707</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000123905116001</t>
+          <t>20208000596207831001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №3986 10.08.2026, QQS bilan</t>
+          <t>Предоплата за материалы по договору №37/26</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3326,33 +3326,33 @@
           <t>168</t>
         </is>
       </c>
-      <c r="C78" s="2" t="n"/>
-      <c r="D78" s="2" t="n">
-        <v>14846000</v>
-      </c>
+      <c r="C78" s="2" t="n">
+        <v>10807000</v>
+      </c>
+      <c r="D78" s="2" t="n"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Tong Tikuv MChJ</t>
+          <t>Nurafshon Sut Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>280547772</t>
+          <t>282958707</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000712235315001</t>
+          <t>20208000596207831001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №155/26, QQS 12%</t>
+          <t>MATERIALLAR UCHUN OLDINDAN TO'LOV, SHARTNOMA №225/26</t>
         </is>
       </c>
     </row>
@@ -3369,31 +3369,31 @@
       </c>
       <c r="C79" s="2" t="n"/>
       <c r="D79" s="2" t="n">
-        <v>10268000</v>
+        <v>80302000</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Buxoro Farm Savdo XK</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>346112208</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000164280529001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8097 10.08.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №296/26 от 10.08.2026</t>
         </is>
       </c>
     </row>
@@ -3408,33 +3408,33 @@
           <t>170</t>
         </is>
       </c>
-      <c r="C80" s="2" t="n"/>
-      <c r="D80" s="2" t="n">
-        <v>5722000</v>
-      </c>
+      <c r="C80" s="2" t="n">
+        <v>4630000</v>
+      </c>
+      <c r="D80" s="2" t="n"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Yangi Hayot Qurilish MChJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>281427108</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000189581100001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3728</t>
+          <t>Аренда помещения за агуст, дог. №34/20</t>
         </is>
       </c>
     </row>
@@ -3450,32 +3450,32 @@
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>4630000</v>
+        <v>5728000</v>
       </c>
       <c r="D81" s="2" t="n"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Zafar Qurilish Materiallari MChJ</t>
+          <t>Bog'ishamol Metall XK</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>378144144</t>
+          <t>300463501</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000702827779001</t>
+          <t>20208000591046906001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Ijara haqi avgust oyi uchun, shartn. №6/25</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №47/26, QQS bilan</t>
         </is>
       </c>
     </row>
@@ -3491,32 +3491,32 @@
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>12216000</v>
+        <v>9930000</v>
       </c>
       <c r="D82" s="2" t="n"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Chirchiq Qurilish MChJ</t>
+          <t>Bog'ishamol Metall XK</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>306978170</t>
+          <t>300463501</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000935712209001</t>
+          <t>20208000591046906001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №162/26, QQS bilan</t>
+          <t>Оплата за товары согласно счет-фактуре №8460</t>
         </is>
       </c>
     </row>
@@ -3532,32 +3532,32 @@
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>175603000</v>
+        <v>112186000</v>
       </c>
       <c r="D83" s="2" t="n"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Mehnat Mebel MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>280843314</t>
+          <t>241127198</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000711222925001</t>
+          <t>20208000948653694001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №8626</t>
+          <t>Оплата за товары согласно с/ф №7969</t>
         </is>
       </c>
     </row>
@@ -3574,38 +3574,38 @@
       </c>
       <c r="C84" s="2" t="n"/>
       <c r="D84" s="2" t="n">
-        <v>6371000</v>
+        <v>15961000</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Shartnoma №69/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по договору №69/26 от 11.08.2026</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>12.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3615,31 +3615,31 @@
       </c>
       <c r="C85" s="2" t="n"/>
       <c r="D85" s="2" t="n">
-        <v>34593000</v>
+        <v>6081000</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Afrosiyob Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>254777237</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000223531516001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №211/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №656 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -3654,40 +3654,40 @@
           <t>176</t>
         </is>
       </c>
-      <c r="C86" s="2" t="n">
-        <v>63457000</v>
-      </c>
-      <c r="D86" s="2" t="n"/>
+      <c r="C86" s="2" t="n"/>
+      <c r="D86" s="2" t="n">
+        <v>6005000</v>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Xiva Savdo AJ</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>276141163</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000172772008001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №143/26</t>
+          <t>Оплата за товар по счет-фактуре №7454 от 12.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>13.08.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3696,39 +3696,39 @@
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>152429000</v>
+        <v>23220000</v>
       </c>
       <c r="D87" s="2" t="n"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Chirchiq Qurilish MChJ</t>
+          <t>Shahrisabz Meva-Sabzavot AJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>306978170</t>
+          <t>244144970</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000935712209001</t>
+          <t>20208000827779009001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №180/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №2239</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3736,33 +3736,33 @@
           <t>178</t>
         </is>
       </c>
-      <c r="C88" s="2" t="n"/>
-      <c r="D88" s="2" t="n">
-        <v>65876000</v>
-      </c>
+      <c r="C88" s="2" t="n">
+        <v>230860000</v>
+      </c>
+      <c r="D88" s="2" t="n"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Shahrisabz Meva-Sabzavot AJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>244144970</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000827779009001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6115 14.08.2026, QQS bilan</t>
+          <t>Оплата за транспортные услуги по дог. №247/26</t>
         </is>
       </c>
     </row>
@@ -3777,33 +3777,33 @@
           <t>179</t>
         </is>
       </c>
-      <c r="C89" s="2" t="n"/>
-      <c r="D89" s="2" t="n">
-        <v>33331000</v>
-      </c>
+      <c r="C89" s="2" t="n">
+        <v>24353000</v>
+      </c>
+      <c r="D89" s="2" t="n"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ilhom Agro Servis MChJ</t>
+          <t>Bog'ishamol Metall XK</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>246491058</t>
+          <t>300463501</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000123905116001</t>
+          <t>20208000591046906001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №3943 14.08.2026, QQS bilan</t>
+          <t>Предоплата за материалы по дог. №222/26</t>
         </is>
       </c>
     </row>
@@ -3820,31 +3820,31 @@
       </c>
       <c r="C90" s="2" t="n"/>
       <c r="D90" s="2" t="n">
-        <v>9294000</v>
+        <v>37996000</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №7534 за поставленный товар</t>
+          <t>Оплата по с/ф №8263 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -3861,31 +3861,31 @@
       </c>
       <c r="C91" s="2" t="n"/>
       <c r="D91" s="2" t="n">
-        <v>7393000</v>
+        <v>29886000</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Shartnoma №123/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по договору №123/26 от 17.08.2026</t>
         </is>
       </c>
     </row>
@@ -3902,31 +3902,31 @@
       </c>
       <c r="C92" s="2" t="n"/>
       <c r="D92" s="2" t="n">
-        <v>6732000</v>
+        <v>6312000</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Tong Tikuv MChJ</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>280547772</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000712235315001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5655 17.08.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №193/26 т 17.08.2026</t>
         </is>
       </c>
     </row>
@@ -3941,33 +3941,33 @@
           <t>183</t>
         </is>
       </c>
-      <c r="C93" s="2" t="n">
-        <v>3597000</v>
-      </c>
-      <c r="D93" s="2" t="n"/>
+      <c r="C93" s="2" t="n"/>
+      <c r="D93" s="2" t="n">
+        <v>5411000</v>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq iyul 2026</t>
+          <t>Оплата по с/ф №3570 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -4008,14 +4008,14 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Jismoniy shaxslar daromad solig'i iyul 2026</t>
+          <t>Социальный налог за июль 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4023,40 +4023,40 @@
           <t>185</t>
         </is>
       </c>
-      <c r="C95" s="2" t="n"/>
-      <c r="D95" s="2" t="n">
-        <v>64180000</v>
-      </c>
+      <c r="C95" s="2" t="n">
+        <v>3597000</v>
+      </c>
+      <c r="D95" s="2" t="n"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>241049441</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000864703882001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7880</t>
+          <t>Налог на доходы физических лиц за июль 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4064,40 +4064,40 @@
           <t>186</t>
         </is>
       </c>
-      <c r="C96" s="2" t="n"/>
-      <c r="D96" s="2" t="n">
-        <v>17143000</v>
-      </c>
+      <c r="C96" s="2" t="n">
+        <v>14709000</v>
+      </c>
+      <c r="D96" s="2" t="n"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Shodlik Metall MChJ</t>
+          <t>Nurafshon Sut Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>321585707</t>
+          <t>282958707</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000496060022001</t>
+          <t>20208000596207831001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №4/26, QQS 12%</t>
+          <t>Оплата за транспортные услуги по договору №280/26</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4105,35 +4105,40 @@
           <t>187</t>
         </is>
       </c>
-      <c r="C97" s="2" t="n">
-        <v>42000000</v>
-      </c>
-      <c r="D97" s="2" t="n"/>
+      <c r="C97" s="2" t="n"/>
+      <c r="D97" s="2" t="n">
+        <v>55211000</v>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-0391)</t>
+          <t>Shodlik Qog'oz MChJ</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>16307000368529438417</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-0391 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Оплата за продукцию по договору №179/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4143,38 +4148,38 @@
       </c>
       <c r="C98" s="2" t="n"/>
       <c r="D98" s="2" t="n">
-        <v>8782000</v>
+        <v>9311000</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Tong Tikuv MChJ</t>
+          <t>Afrosiyob Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>280547772</t>
+          <t>254777237</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000712235315001</t>
+          <t>20208000223531516001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Shartnoma №116/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за продукци по договору №3/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4184,38 +4189,38 @@
       </c>
       <c r="C99" s="2" t="n"/>
       <c r="D99" s="2" t="n">
-        <v>71135000</v>
+        <v>6818000</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Guliston Metall Servis MChJ</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>375524438</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000001652700001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Shartnoma №19/26 bo'yicha oldindan to'lov</t>
+          <t>Yetkazilgantovar uchun to'lov h/f №907</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4223,40 +4228,40 @@
           <t>190</t>
         </is>
       </c>
-      <c r="C100" s="2" t="n"/>
-      <c r="D100" s="2" t="n">
-        <v>6811000</v>
-      </c>
+      <c r="C100" s="2" t="n">
+        <v>5264000</v>
+      </c>
+      <c r="D100" s="2" t="n"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Nurafshon Sut Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>282958707</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000596207831001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №902</t>
+          <t>Оплата за транспортные услуги по дог. №267/26</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4265,39 +4270,39 @@
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>2894000</v>
+        <v>17973000</v>
       </c>
       <c r="D101" s="2" t="n"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Shahrisabz Meva-Sabzavot AJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>244144970</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000094468700001</t>
+          <t>20208000827779009001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>Предоплата за материалы по дог. №129/26</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4305,40 +4310,40 @@
           <t>192</t>
         </is>
       </c>
-      <c r="C102" s="2" t="n">
-        <v>7820000</v>
-      </c>
-      <c r="D102" s="2" t="n"/>
+      <c r="C102" s="2" t="n"/>
+      <c r="D102" s="2" t="n">
+        <v>4749000</v>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Zarafshon Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>258570744</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000606002244001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>QO'SHILGAN QIYMAT SOLIG'I IYUL OYI</t>
+          <t>Оплата за продукцию по договору №4/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4347,22 +4352,17 @@
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>24613000</v>
+        <v>42000000</v>
       </c>
       <c r="D103" s="2" t="n"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Xiva Savdo AJ</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>276141163</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-0391)</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000172772008001</t>
+          <t>16307000368529438417</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4372,14 +4372,14 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГОВОРУ №139/26</t>
+          <t>Kredit shartnomasi L-2025-0391 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4389,38 +4389,38 @@
       </c>
       <c r="C104" s="2" t="n"/>
       <c r="D104" s="2" t="n">
-        <v>24476000</v>
+        <v>94254000</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Afrosiyob Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>254777237</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000223531516001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №2375 26.08.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №116/26 от 21.08.2026</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4430,38 +4430,38 @@
       </c>
       <c r="C105" s="2" t="n"/>
       <c r="D105" s="2" t="n">
-        <v>10881000</v>
+        <v>14022000</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Afrosiyob Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>254777237</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000223531516001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №296/26 от 31.08.2026</t>
+          <t>Mahsulot uchun to'lov, shartnoma №150/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4469,35 +4469,40 @@
           <t>196</t>
         </is>
       </c>
-      <c r="C106" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D106" s="2" t="n"/>
+      <c r="C106" s="2" t="n"/>
+      <c r="D106" s="2" t="n">
+        <v>8320000</v>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Shodlik Qog'oz MChJ</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
+          <t>Оплата по счет-фактуре №5122 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4506,39 +4511,39 @@
         </is>
       </c>
       <c r="C107" s="2" t="n">
-        <v>13906000</v>
+        <v>7895000</v>
       </c>
       <c r="D107" s="2" t="n"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Chirchiq Qurilish MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>306978170</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000935712209001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №261/26</t>
+          <t>НДС за июль 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4546,40 +4551,40 @@
           <t>198</t>
         </is>
       </c>
-      <c r="C108" s="2" t="n">
-        <v>18003000</v>
-      </c>
-      <c r="D108" s="2" t="n"/>
+      <c r="C108" s="2" t="n"/>
+      <c r="D108" s="2" t="n">
+        <v>13785000</v>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Mehnat Mebel MChJ</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>280843314</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000711222925001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Transpor xizmatlari uchun to'lov, shartnoma №282/26</t>
+          <t>Предоплата за товар по договору №146/26 от 24.08.2026</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4587,40 +4592,40 @@
           <t>199</t>
         </is>
       </c>
-      <c r="C109" s="2" t="n">
-        <v>2151000</v>
-      </c>
-      <c r="D109" s="2" t="n"/>
+      <c r="C109" s="2" t="n"/>
+      <c r="D109" s="2" t="n">
+        <v>9082000</v>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Chirchiq Qurilish MChJ</t>
+          <t>Shahrisabz Mato XK</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>306978170</t>
+          <t>314116341</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000935712209001</t>
+          <t>20208000277200827001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №4754</t>
+          <t>Оплата по счет-фактуре №2394 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4628,40 +4633,40 @@
           <t>200</t>
         </is>
       </c>
-      <c r="C110" s="2" t="n">
-        <v>2789000</v>
-      </c>
-      <c r="D110" s="2" t="n"/>
+      <c r="C110" s="2" t="n"/>
+      <c r="D110" s="2" t="n">
+        <v>8027000</v>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Chirchiq Qurilish MChJ</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>306978170</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000935712209001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №193/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №147/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4671,38 +4676,38 @@
       </c>
       <c r="C111" s="2" t="n"/>
       <c r="D111" s="2" t="n">
-        <v>7217000</v>
+        <v>4464000</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Guliston Metall Servis MChJ</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>375524438</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000001652700001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №197/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №902 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4710,40 +4715,40 @@
           <t>202</t>
         </is>
       </c>
-      <c r="C112" s="2" t="n"/>
-      <c r="D112" s="2" t="n">
-        <v>3727000</v>
-      </c>
+      <c r="C112" s="2" t="n">
+        <v>2894000</v>
+      </c>
+      <c r="D112" s="2" t="n"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Ilhom Agro Servis MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>246491058</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000123905116001</t>
+          <t>20208000818188088001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №189/26, QQS 12%</t>
+          <t>Оплата за электрэнергию согласно счету</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4752,39 +4757,39 @@
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>7440000</v>
+        <v>7946000</v>
       </c>
       <c r="D113" s="2" t="n"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Chirchiq Qurilish MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>306978170</t>
+          <t>241127198</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000935712209001</t>
+          <t>20208000948653694001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №106/26, QQS bilan</t>
+          <t>Оплата за товары согласно счет-фактуре №1169</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4793,39 +4798,39 @@
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>33471000</v>
+        <v>16028000</v>
       </c>
       <c r="D114" s="2" t="n"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Chirchiq Qurilish MChJ</t>
+          <t>Shahrisabz Meva-Sabzavot AJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>306978170</t>
+          <t>244144970</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000935712209001</t>
+          <t>20208000827779009001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №174/26</t>
+          <t>Оплата за транспортные услуги по дог. №159/26</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4833,40 +4838,40 @@
           <t>205</t>
         </is>
       </c>
-      <c r="C115" s="2" t="n">
-        <v>4747000</v>
-      </c>
-      <c r="D115" s="2" t="n"/>
+      <c r="C115" s="2" t="n"/>
+      <c r="D115" s="2" t="n">
+        <v>5942000</v>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Mehnat Mebel MChJ</t>
+          <t>Zarafshon Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>280843314</t>
+          <t>397817069</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000711222925001</t>
+          <t>20208000571220901001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №172/26 от 04.09.2026, НДС 12%</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №267/26 ОТ 27.08.2026</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4876,38 +4881,38 @@
       </c>
       <c r="C116" s="2" t="n"/>
       <c r="D116" s="2" t="n">
-        <v>79434000</v>
+        <v>4846000</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Afrosiyob Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>254777237</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000223531516001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4247 за поставленный товар</t>
+          <t>Оплата по счет-фактуре №5304 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4917,38 +4922,38 @@
       </c>
       <c r="C117" s="2" t="n"/>
       <c r="D117" s="2" t="n">
-        <v>15377000</v>
+        <v>149826000</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5759</t>
+          <t>Оплата за товар по счет-фактуре №23 от 31.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4958,38 +4963,38 @@
       </c>
       <c r="C118" s="2" t="n"/>
       <c r="D118" s="2" t="n">
-        <v>9530000</v>
+        <v>22945000</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Afrosiyob Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>254777237</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000223531516001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Shartnoma №199/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по договору №228/26 от 31.08.2026</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4997,23 +5002,18 @@
           <t>209</t>
         </is>
       </c>
-      <c r="C119" s="2" t="n"/>
-      <c r="D119" s="2" t="n">
-        <v>6302000</v>
-      </c>
+      <c r="C119" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D119" s="2" t="n"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>328917343</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5023,14 +5023,14 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №28/26, QQS 12%</t>
+          <t>Плата за SMS-информирование</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5039,39 +5039,39 @@
         </is>
       </c>
       <c r="C120" s="2" t="n">
-        <v>4947000</v>
+        <v>5620000</v>
       </c>
       <c r="D120" s="2" t="n"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Zafar Qurilish Materiallari MChJ</t>
+          <t>Bog'ishamol Metall XK</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>378144144</t>
+          <t>300463501</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000702827779001</t>
+          <t>20208000591046906001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Ijara haqi sentyabr oyi uchun, shartnoma №6/25</t>
+          <t>Предоплата за материалы по договору №100/26</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5080,34 +5080,39 @@
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>28180000</v>
+        <v>10193000</v>
       </c>
       <c r="D121" s="2" t="n"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Bog'ishamol Metall XK</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>300463501</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000591046906001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi avgust 2026 (plastik kartalarga)</t>
+          <t>Оплата за транспортные услуги по договору №119/26</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5116,39 +5121,39 @@
         </is>
       </c>
       <c r="C122" s="2" t="n">
-        <v>44639000</v>
+        <v>14582000</v>
       </c>
       <c r="D122" s="2" t="n"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Xiva Savdo AJ</t>
+          <t>Bog'ishamol Metall XK</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>276141163</t>
+          <t>300463501</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000172772008001</t>
+          <t>20208000591046906001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №104/26</t>
+          <t>Оплата за сырье по договору №1/26 от 31.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5157,39 +5162,39 @@
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>309286000</v>
+        <v>19148000</v>
       </c>
       <c r="D123" s="2" t="n"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Mehnat Mebel MChJ</t>
+          <t>Shahrisabz Meva-Sabzavot AJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>280843314</t>
+          <t>244144970</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000711222925001</t>
+          <t>20208000827779009001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №95/26</t>
+          <t>Оплата за сырье по договору№285/26 от 31.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
+          <t>03.09.2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5199,21 +5204,21 @@
       </c>
       <c r="C124" s="2" t="n"/>
       <c r="D124" s="2" t="n">
-        <v>12158000</v>
+        <v>28252000</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Namangan Yog'och MChJ</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>217915651</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000496888330001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5223,14 +5228,14 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Shartnoma №45/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №5474 от 03.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
+          <t>03.09.2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5240,38 +5245,38 @@
       </c>
       <c r="C125" s="2" t="n"/>
       <c r="D125" s="2" t="n">
-        <v>4053000</v>
+        <v>3721000</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7814 08.09.2026, QQS bilan</t>
+          <t>Предоплата за товар по дог. №174/26 от 03.09.2026</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
+          <t>03.09.2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5280,39 +5285,39 @@
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>2001000</v>
+        <v>16151000</v>
       </c>
       <c r="D126" s="2" t="n"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Chirchiq Qurilish MChJ</t>
+          <t>Shahrisabz Meva-Sabzavot AJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>306978170</t>
+          <t>244144970</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000935712209001</t>
+          <t>20208000827779009001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №196/26</t>
+          <t>Оплата за сырье по договору №230/26 от 03.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5320,23 +5325,18 @@
           <t>217</t>
         </is>
       </c>
-      <c r="C127" s="2" t="n"/>
-      <c r="D127" s="2" t="n">
-        <v>5780000</v>
-      </c>
+      <c r="C127" s="2" t="n">
+        <v>28180000</v>
+      </c>
+      <c r="D127" s="2" t="n"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>328917343</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5346,14 +5346,14 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №536 от 09.09.2026, в т.ч. НДС 12%</t>
+          <t>Перечисление заработной платы за август 2026 г. согласно реестру №2362</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5361,40 +5361,40 @@
           <t>218</t>
         </is>
       </c>
-      <c r="C128" s="2" t="n"/>
-      <c r="D128" s="2" t="n">
-        <v>4056000</v>
-      </c>
+      <c r="C128" s="2" t="n">
+        <v>62039000</v>
+      </c>
+      <c r="D128" s="2" t="n"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Tong Tikuv MChJ</t>
+          <t>Bog'ishamol Metall XK</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>280547772</t>
+          <t>300463501</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000712235315001</t>
+          <t>20208000591046906001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №15/26, QQS 12%</t>
+          <t>Оплата за сырье по договору №22/26 от 04.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5402,40 +5402,40 @@
           <t>219</t>
         </is>
       </c>
-      <c r="C129" s="2" t="n"/>
-      <c r="D129" s="2" t="n">
-        <v>3815000</v>
-      </c>
+      <c r="C129" s="2" t="n">
+        <v>67014000</v>
+      </c>
+      <c r="D129" s="2" t="n"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Tong Tikuv MChJ</t>
+          <t>Shahrisabz Meva-Sabzavot AJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>280547772</t>
+          <t>244144970</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000712235315001</t>
+          <t>20208000827779009001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №2003 10.09.2026, QQS bilan</t>
+          <t>Оплата за транспортные услуги по договору №89/26</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5443,40 +5443,40 @@
           <t>220</t>
         </is>
       </c>
-      <c r="C130" s="2" t="n">
-        <v>8496000</v>
-      </c>
-      <c r="D130" s="2" t="n"/>
+      <c r="C130" s="2" t="n"/>
+      <c r="D130" s="2" t="n">
+        <v>41692000</v>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Xiva Savdo AJ</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>276141163</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000172772008001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №122/26, QQS bilan</t>
+          <t>Оплата по с/ф №5759 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5484,40 +5484,40 @@
           <t>221</t>
         </is>
       </c>
-      <c r="C131" s="2" t="n">
-        <v>132230000</v>
-      </c>
-      <c r="D131" s="2" t="n"/>
+      <c r="C131" s="2" t="n"/>
+      <c r="D131" s="2" t="n">
+        <v>37890000</v>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Chirchiq Qurilish MChJ</t>
+          <t>Qarshi Mato XK</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>306978170</t>
+          <t>253037731</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000935712209001</t>
+          <t>20208000094103219001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №279/26</t>
+          <t>Предоплата за товар по договору №262/26 от 07.09.2026</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5527,38 +5527,38 @@
       </c>
       <c r="C132" s="2" t="n"/>
       <c r="D132" s="2" t="n">
-        <v>13558000</v>
+        <v>11742000</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Tong Tikuv MChJ</t>
+          <t>Nihol Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>280547772</t>
+          <t>391565114</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000712235315001</t>
+          <t>20208000688833047001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №275/26, QQS 12%</t>
+          <t>Предоплата за товар по договору №104/26 от 07.09.2026</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5568,38 +5568,38 @@
       </c>
       <c r="C133" s="2" t="n"/>
       <c r="D133" s="2" t="n">
-        <v>10484000</v>
+        <v>9084000</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №115/26, QQS 12%</t>
+          <t>Предоплата за товар по дог. №199/26 от 07.09.2026</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5609,38 +5609,38 @@
       </c>
       <c r="C134" s="2" t="n"/>
       <c r="D134" s="2" t="n">
-        <v>6017000</v>
+        <v>8618000</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Mahsuot uchun to'lov, shartnoma №32/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №28/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5649,39 +5649,39 @@
         </is>
       </c>
       <c r="C135" s="2" t="n">
-        <v>2258000</v>
+        <v>11405000</v>
       </c>
       <c r="D135" s="2" t="n"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Chirchiq Qurilish MChJ</t>
+          <t>Shahrisabz Meva-Sabzavot AJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>306978170</t>
+          <t>244144970</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000935712209001</t>
+          <t>20208000827779009001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №227/26</t>
+          <t>Оплата за транспортные услуги по договору №89/26</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5689,40 +5689,40 @@
           <t>226</t>
         </is>
       </c>
-      <c r="C136" s="2" t="n">
-        <v>9834000</v>
-      </c>
-      <c r="D136" s="2" t="n"/>
+      <c r="C136" s="2" t="n"/>
+      <c r="D136" s="2" t="n">
+        <v>12656000</v>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Chirchiq Qurilish MChJ</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>306978170</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000935712209001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №119/26</t>
+          <t>Tovar uchun to'lov, h/f №536 09.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5731,39 +5731,39 @@
         </is>
       </c>
       <c r="C137" s="2" t="n">
-        <v>20891000</v>
+        <v>4947000</v>
       </c>
       <c r="D137" s="2" t="n"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Xiva Savdo AJ</t>
+          <t>Yangi Hayot Qurilish MChJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>276141163</t>
+          <t>281427108</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000172772008001</t>
+          <t>20208000189581100001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №6037</t>
+          <t>Арендная плата за сентябрь 2026 г. по ог. №34/20</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5771,40 +5771,40 @@
           <t>228</t>
         </is>
       </c>
-      <c r="C138" s="2" t="n"/>
-      <c r="D138" s="2" t="n">
-        <v>4600000</v>
-      </c>
+      <c r="C138" s="2" t="n">
+        <v>11534000</v>
+      </c>
+      <c r="D138" s="2" t="n"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Navro'z Avto Ehtiyot XK</t>
+          <t>Nurafshon Sut Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>270530377</t>
+          <t>282958707</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000120941032001</t>
+          <t>20208000596207831001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3588</t>
+          <t>Оплата за транспортные услуги по договору №186/26</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5814,38 +5814,38 @@
       </c>
       <c r="C139" s="2" t="n"/>
       <c r="D139" s="2" t="n">
-        <v>6133000</v>
+        <v>44534000</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Shahrisabz Mato XK</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>314116341</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000277200827001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Shartnoma №203/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №248/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5855,38 +5855,38 @@
       </c>
       <c r="C140" s="2" t="n"/>
       <c r="D140" s="2" t="n">
-        <v>3979000</v>
+        <v>15244000</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Xiva Un Mahsulotlari XK</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>319806600</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000862164743001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1785 16.09.2026, QQS bilan</t>
+          <t>Оплат за продукцию по договору №32/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5894,40 +5894,40 @@
           <t>231</t>
         </is>
       </c>
-      <c r="C141" s="2" t="n">
-        <v>3843000</v>
-      </c>
-      <c r="D141" s="2" t="n"/>
+      <c r="C141" s="2" t="n"/>
+      <c r="D141" s="2" t="n">
+        <v>11682000</v>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Avgust oyi uchun ijtimoiy soliq</t>
+          <t>Оплата по счет-фактуре №23 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5935,40 +5935,40 @@
           <t>232</t>
         </is>
       </c>
-      <c r="C142" s="2" t="n">
-        <v>3843000</v>
-      </c>
-      <c r="D142" s="2" t="n"/>
+      <c r="C142" s="2" t="n"/>
+      <c r="D142" s="2" t="n">
+        <v>4513000</v>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Jismoniy shaxslar daromad solig'i avgust 2026</t>
+          <t>Оплата за продукцию по договору №115/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5977,39 +5977,39 @@
         </is>
       </c>
       <c r="C143" s="2" t="n">
-        <v>7732000</v>
+        <v>3843000</v>
       </c>
       <c r="D143" s="2" t="n"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Chirchiq Qurilish MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>306978170</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000935712209001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №3172</t>
+          <t>УПЛАТА СОЦИАЛЬНОГО НАЛОГА ЗА АВГУСТ</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>17.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6017,40 +6017,40 @@
           <t>234</t>
         </is>
       </c>
-      <c r="C144" s="2" t="n"/>
-      <c r="D144" s="2" t="n">
-        <v>10324000</v>
-      </c>
+      <c r="C144" s="2" t="n">
+        <v>3843000</v>
+      </c>
+      <c r="D144" s="2" t="n"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9190 17.09.2026, QQS bilan</t>
+          <t>JShDS avgust oyi uchun</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>17.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6058,40 +6058,40 @@
           <t>235</t>
         </is>
       </c>
-      <c r="C145" s="2" t="n"/>
-      <c r="D145" s="2" t="n">
-        <v>8627000</v>
-      </c>
+      <c r="C145" s="2" t="n">
+        <v>131479000</v>
+      </c>
+      <c r="D145" s="2" t="n"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Shahrisabz Meva-Sabzavot AJ</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>244144970</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000827779009001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №275/26, QQS 12%</t>
+          <t>Tovarlar uchun to'lov h/f №3158</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>18.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6101,21 +6101,21 @@
       </c>
       <c r="C146" s="2" t="n"/>
       <c r="D146" s="2" t="n">
-        <v>43364000</v>
+        <v>31686000</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Namangan Yog'och MChJ</t>
+          <t>Qarshi Mato XK</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>217915651</t>
+          <t>253037731</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000496888330001</t>
+          <t>20208000094103219001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6125,14 +6125,14 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №175/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №3588 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>18.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6140,40 +6140,40 @@
           <t>237</t>
         </is>
       </c>
-      <c r="C147" s="2" t="n"/>
-      <c r="D147" s="2" t="n">
-        <v>3655000</v>
-      </c>
+      <c r="C147" s="2" t="n">
+        <v>60902000</v>
+      </c>
+      <c r="D147" s="2" t="n"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Bog'ishamol Metall XK</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>300463501</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000591046906001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №134/26, QQS 12%</t>
+          <t>Предоплата за материалы по договору №196/26</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>20.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6181,35 +6181,40 @@
           <t>238</t>
         </is>
       </c>
-      <c r="C148" s="2" t="n">
-        <v>42000000</v>
-      </c>
-      <c r="D148" s="2" t="n"/>
+      <c r="C148" s="2" t="n"/>
+      <c r="D148" s="2" t="n">
+        <v>81572000</v>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-0391)</t>
+          <t>Shodlik Qog'oz MChJ</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>16307000368529438417</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-0391 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Предоплата за товар по договору №203/26 от 16.09.2026</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6219,38 +6224,38 @@
       </c>
       <c r="C149" s="2" t="n"/>
       <c r="D149" s="2" t="n">
-        <v>7652000</v>
+        <v>10638000</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №7489 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №1105 от 16.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6258,23 +6263,23 @@
           <t>240</t>
         </is>
       </c>
-      <c r="C150" s="2" t="n"/>
-      <c r="D150" s="2" t="n">
-        <v>7161000</v>
-      </c>
+      <c r="C150" s="2" t="n">
+        <v>21498000</v>
+      </c>
+      <c r="D150" s="2" t="n"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Guliston Metall Servis MChJ</t>
+          <t>Nurafshon Sut Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>375524438</t>
+          <t>282958707</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>20208000001652700001</t>
+          <t>20208000596207831001</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -6284,14 +6289,14 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9660 от 21.09.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за материалы по договору №10/26</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6299,40 +6304,40 @@
           <t>241</t>
         </is>
       </c>
-      <c r="C151" s="2" t="n">
-        <v>5534000</v>
-      </c>
-      <c r="D151" s="2" t="n"/>
+      <c r="C151" s="2" t="n"/>
+      <c r="D151" s="2" t="n">
+        <v>5370000</v>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Xiva Savdo AJ</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>276141163</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20208000172772008001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №146/26</t>
+          <t>Оплата за продукцию по договору №275/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>22.09.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6340,40 +6345,40 @@
           <t>242</t>
         </is>
       </c>
-      <c r="C152" s="2" t="n"/>
-      <c r="D152" s="2" t="n">
-        <v>30943000</v>
-      </c>
+      <c r="C152" s="2" t="n">
+        <v>29595000</v>
+      </c>
+      <c r="D152" s="2" t="n"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Navoiy Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>390107567</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000876402081001</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №498</t>
+          <t>Оплата за товары согласно счет-фактуре №7890</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>22.09.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -6381,40 +6386,40 @@
           <t>243</t>
         </is>
       </c>
-      <c r="C153" s="2" t="n"/>
-      <c r="D153" s="2" t="n">
-        <v>4042000</v>
-      </c>
+      <c r="C153" s="2" t="n">
+        <v>53984000</v>
+      </c>
+      <c r="D153" s="2" t="n"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Shahrisabz Meva-Sabzavot AJ</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>244144970</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000827779009001</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4183 за поставленный товар</t>
+          <t>Оплата за товары согласно счет-фактуре №4065</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>23.09.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -6424,21 +6429,21 @@
       </c>
       <c r="C154" s="2" t="n"/>
       <c r="D154" s="2" t="n">
-        <v>16533000</v>
+        <v>25061000</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Namangan Yog'och MChJ</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>217915651</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>20208000496888330001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -6448,14 +6453,14 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №226/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №134/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>23.09.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -6465,38 +6470,38 @@
       </c>
       <c r="C155" s="2" t="n"/>
       <c r="D155" s="2" t="n">
-        <v>16441000</v>
+        <v>6751000</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Nihol Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>391565114</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000688833047001</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №249/26, QQS 12%</t>
+          <t>Оплата за продукцию по дог. №175/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>23.09.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -6504,23 +6509,23 @@
           <t>246</t>
         </is>
       </c>
-      <c r="C156" s="2" t="n"/>
-      <c r="D156" s="2" t="n">
-        <v>12401000</v>
-      </c>
+      <c r="C156" s="2" t="n">
+        <v>26271000</v>
+      </c>
+      <c r="D156" s="2" t="n"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Namangan Yog'och MChJ</t>
+          <t>Shahrisabz Meva-Sabzavot AJ</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>217915651</t>
+          <t>244144970</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>20208000496888330001</t>
+          <t>20208000827779009001</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -6530,14 +6535,14 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6964 23.09.2026, QQS bilan</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №201/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>23.09.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -6545,40 +6550,40 @@
           <t>247</t>
         </is>
       </c>
-      <c r="C157" s="2" t="n"/>
-      <c r="D157" s="2" t="n">
-        <v>7413000</v>
-      </c>
+      <c r="C157" s="2" t="n">
+        <v>42390000</v>
+      </c>
+      <c r="D157" s="2" t="n"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Bog'ishamol Metall XK</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>300463501</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000591046906001</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2631</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №10/26</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>23.09.2026</t>
+          <t>20.09.2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -6587,39 +6592,34 @@
         </is>
       </c>
       <c r="C158" s="2" t="n">
-        <v>7899000</v>
+        <v>42000000</v>
       </c>
       <c r="D158" s="2" t="n"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>201122905</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-0391)</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>16307000368529438417</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>QQS avgust 2026 uchun</t>
+          <t>Kredit shartnomasi L-2025-0391 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>24.09.2026</t>
+          <t>22.09.2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -6629,38 +6629,38 @@
       </c>
       <c r="C159" s="2" t="n"/>
       <c r="D159" s="2" t="n">
-        <v>10414000</v>
+        <v>55282000</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №245/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №498 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>25.09.2026</t>
+          <t>22.09.2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -6670,38 +6670,38 @@
       </c>
       <c r="C160" s="2" t="n"/>
       <c r="D160" s="2" t="n">
-        <v>17244000</v>
+        <v>10463000</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №189/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4183</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>25.09.2026</t>
+          <t>23.09.2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -6711,38 +6711,38 @@
       </c>
       <c r="C161" s="2" t="n"/>
       <c r="D161" s="2" t="n">
-        <v>12814000</v>
+        <v>210644000</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Nihol Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>391565114</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000688833047001</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №50/26 от 25.09.2026</t>
+          <t>Оплата за товар по счет-фактуре №6964 от 23.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>25.09.2026</t>
+          <t>23.09.2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -6751,39 +6751,39 @@
         </is>
       </c>
       <c r="C162" s="2" t="n">
-        <v>3092000</v>
+        <v>8298000</v>
       </c>
       <c r="D162" s="2" t="n"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>20208000094468700001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov sentyabr</t>
+          <t>QQS avgust 2026 uchun</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>24.09.2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -6791,40 +6791,40 @@
           <t>253</t>
         </is>
       </c>
-      <c r="C163" s="2" t="n"/>
-      <c r="D163" s="2" t="n">
-        <v>163477000</v>
-      </c>
+      <c r="C163" s="2" t="n">
+        <v>3092000</v>
+      </c>
+      <c r="D163" s="2" t="n"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000818188088001</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9102 28.09.2026, QQS bilan</t>
+          <t>ОПЛАТА ЗА ЭЛЕКТРОЭНЕРГИЮ СОГЛАСНО СЧЕТУ</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>25.09.2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -6834,38 +6834,38 @@
       </c>
       <c r="C164" s="2" t="n"/>
       <c r="D164" s="2" t="n">
-        <v>15664000</v>
+        <v>7445000</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Guliston Metall Servis MChJ</t>
+          <t>Afrosiyob Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>375524438</t>
+          <t>254777237</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>20208000001652700001</t>
+          <t>20208000223531516001</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1384</t>
+          <t>Оплата за товар по счет-фактуре №6300 от 25.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>25.09.2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -6875,31 +6875,31 @@
       </c>
       <c r="C165" s="2" t="n"/>
       <c r="D165" s="2" t="n">
-        <v>10021000</v>
+        <v>5054000</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Shodlik Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>391734348</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000547722704001</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7201 28.09.2026, QQS bilan</t>
+          <t>Shartnoma №50/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
@@ -6914,33 +6914,33 @@
           <t>256</t>
         </is>
       </c>
-      <c r="C166" s="2" t="n"/>
-      <c r="D166" s="2" t="n">
-        <v>7217000</v>
-      </c>
+      <c r="C166" s="2" t="n">
+        <v>18569000</v>
+      </c>
+      <c r="D166" s="2" t="n"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Shahrisabz Meva-Sabzavot AJ</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>244144970</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000827779009001</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4769 28.09.2026, QQS bilan</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №165/26, QQS bilan</t>
         </is>
       </c>
     </row>
@@ -6955,33 +6955,33 @@
           <t>257</t>
         </is>
       </c>
-      <c r="C167" s="2" t="n"/>
-      <c r="D167" s="2" t="n">
-        <v>6998000</v>
-      </c>
+      <c r="C167" s="2" t="n">
+        <v>23318000</v>
+      </c>
+      <c r="D167" s="2" t="n"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>328917343</t>
+          <t>241127198</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>20208000825477227001</t>
+          <t>20208000948653694001</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6423 28.09.2026, QQS bilan</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №112/26</t>
         </is>
       </c>
     </row>
@@ -6997,22 +6997,22 @@
         </is>
       </c>
       <c r="C168" s="2" t="n">
-        <v>1772000</v>
+        <v>25378000</v>
       </c>
       <c r="D168" s="2" t="n"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Chirchiq Qurilish MChJ</t>
+          <t>Nurafshon Sut Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>306978170</t>
+          <t>282958707</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>20208000935712209001</t>
+          <t>20208000596207831001</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -7022,14 +7022,14 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №7593</t>
+          <t>Предоплата за материалы по договору №232/26</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>30.09.2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7037,40 +7037,40 @@
           <t>259</t>
         </is>
       </c>
-      <c r="C169" s="2" t="n">
-        <v>1819000</v>
-      </c>
-      <c r="D169" s="2" t="n"/>
+      <c r="C169" s="2" t="n"/>
+      <c r="D169" s="2" t="n">
+        <v>11893000</v>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Xiva Savdo AJ</t>
+          <t>Gulshan Sut Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>276141163</t>
+          <t>352443850</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>20208000172772008001</t>
+          <t>20208000165270044001</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №97/26</t>
+          <t>Оплата по счет-фактуре №1384 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>30.09.2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7079,22 +7079,17 @@
         </is>
       </c>
       <c r="C170" s="2" t="n">
-        <v>4037000</v>
+        <v>300000</v>
       </c>
       <c r="D170" s="2" t="n"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Xiva Savdo AJ</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>276141163</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>20208000172772008001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -7104,274 +7099,33 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №212/26</t>
+          <t>Bank xizmati uchun komissiya</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="n"/>
-      <c r="D171" s="2" t="n">
-        <v>12726000</v>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>328917343</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>20208000825477227001</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartnoma №110/26, QQS 12%</t>
-        </is>
+          <t>Jami aylanma:</t>
+        </is>
+      </c>
+      <c r="C171" s="4" t="n">
+        <v>2072253000</v>
+      </c>
+      <c r="D171" s="4" t="n">
+        <v>2022853000</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="n"/>
-      <c r="D172" s="2" t="n">
-        <v>12926000</v>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>Tong Tikuv MChJ</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>280547772</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>20208000712235315001</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>Оплата по счет-фактуре №3926 за поставленный товар</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="n"/>
-      <c r="D173" s="2" t="n">
-        <v>11348000</v>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>328917343</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>20208000825477227001</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7672 30.09.2026, QQS bilan</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="n"/>
-      <c r="D174" s="2" t="n">
-        <v>7031000</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>Zarafshon Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>328917343</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>20208000825477227001</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7145 30.09.2026, QQS bilan</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="n"/>
-      <c r="D175" s="2" t="n">
-        <v>5625000</v>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>Xiva Un Mahsulotlari XK</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>319806600</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>20208000862164743001</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7433</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D176" s="2" t="n"/>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>Zarafshon Kredit Bank</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>45994000900000001001</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>Bank xizmati uchun komissiya</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Jami aylanma:</t>
-        </is>
-      </c>
-      <c r="C177" s="4" t="n">
-        <v>2071051000</v>
-      </c>
-      <c r="D177" s="4" t="n">
-        <v>2021651000</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
           <t>Davr oxiridagi qoldiq:</t>
         </is>
       </c>
-      <c r="C178" s="4" t="n">
+      <c r="C172" s="4" t="n">
         <v>92400000</v>
       </c>
-      <c r="D178" s="4" t="n"/>
+      <c r="D172" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
